--- a/trades.xlsx
+++ b/trades.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RMAHDJ\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23A78C0A-A18C-4804-9D43-0D12DE293600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-24735" yWindow="4035" windowWidth="21600" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>TradeID</t>
   </si>
@@ -79,9 +98,6 @@
     <t>T012</t>
   </si>
   <si>
-    <t>BRN Sep26</t>
-  </si>
-  <si>
     <t>BRN Oct26</t>
   </si>
   <si>
@@ -98,16 +114,22 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>31/079/2026  00:00:00</t>
+  </si>
+  <si>
+    <t>BRN Nov26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,13 +167,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,7 +219,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -223,6 +253,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -257,9 +288,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -432,11 +464,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -465,44 +501,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1">
-        <v>46209</v>
+        <v>46280</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>82.15000000000001</v>
+        <v>80.75</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2">
         <v>1000</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1">
-        <v>46211</v>
+        <v>46287</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -511,306 +547,306 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>82.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>1000</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1">
-        <v>46213</v>
+        <v>46294</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>81.90000000000001</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <v>1000</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1">
-        <v>46216</v>
+        <v>46275</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>83.05</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5">
         <v>1000</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
-        <v>46218</v>
+        <v>46282</v>
       </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
       <c r="E6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>80.75</v>
+        <v>82.2</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6">
         <v>1000</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1">
-        <v>46220</v>
+        <v>46289</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>82.2</v>
+        <v>82.95</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>1000</v>
       </c>
       <c r="I7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1">
-        <v>46223</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8">
         <v>1000</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1">
-        <v>46225</v>
+        <v>46271</v>
       </c>
       <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
       <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>82.15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>1000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46273</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10">
         <v>5</v>
       </c>
-      <c r="F9">
-        <v>81.5</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9">
-        <v>1000</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1">
-        <v>46227</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
       <c r="F10">
-        <v>82.95</v>
+        <v>82.6</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10">
         <v>1000</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46278</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>83.05</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11">
+        <v>1000</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46285</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>83.4</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>1000</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1">
-        <v>46230</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11">
-        <v>7</v>
-      </c>
-      <c r="F11">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11">
-        <v>1000</v>
-      </c>
-      <c r="I11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1">
-        <v>46232</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12">
-        <v>6</v>
-      </c>
-      <c r="F12">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12">
-        <v>1000</v>
-      </c>
-      <c r="I12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
       <c r="B13" s="1">
-        <v>46234</v>
+        <v>46292</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F13">
-        <v>83.3</v>
+        <v>84.1</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H13">
         <v>1000</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RMAHDJ\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23A78C0A-A18C-4804-9D43-0D12DE293600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3113499D-DB3C-4535-A62B-967066F34437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24735" yWindow="4035" windowWidth="21600" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30705" yWindow="4650" windowWidth="21600" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
   <si>
     <t>TradeID</t>
   </si>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>USD</t>
-  </si>
-  <si>
-    <t>31/079/2026  00:00:00</t>
   </si>
   <si>
     <t>BRN Nov26</t>
@@ -679,8 +676,8 @@
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
+      <c r="B8" s="1">
+        <v>46289</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
@@ -712,7 +709,7 @@
         <v>46271</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -741,7 +738,7 @@
         <v>46273</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -770,7 +767,7 @@
         <v>46278</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
@@ -799,7 +796,7 @@
         <v>46285</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -828,7 +825,7 @@
         <v>46292</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>

--- a/trades.xlsx
+++ b/trades.xlsx
@@ -8,27 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RMAHDJ\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3113499D-DB3C-4535-A62B-967066F34437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34E77591-F5EB-4B9F-A7AC-DBDA757EDDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30705" yWindow="4650" windowWidth="21600" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5925" yWindow="4080" windowWidth="21600" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -98,6 +85,9 @@
     <t>T012</t>
   </si>
   <si>
+    <t>BRN Sep26</t>
+  </si>
+  <si>
     <t>BRN Oct26</t>
   </si>
   <si>
@@ -114,9 +104,6 @@
   </si>
   <si>
     <t>USD</t>
-  </si>
-  <si>
-    <t>BRN Nov26</t>
   </si>
 </sst>
 </file>
@@ -466,7 +453,6 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -500,42 +486,42 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1">
-        <v>46280</v>
+        <v>46209</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>80.75</v>
+        <v>82.15</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2">
         <v>1000</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
-        <v>46287</v>
+        <v>46211</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
@@ -544,306 +530,306 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>81.5</v>
+        <v>82.6</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3">
         <v>1000</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1">
-        <v>46294</v>
+        <v>46213</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>81.099999999999994</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4">
         <v>1000</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>46275</v>
+        <v>46216</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>81.900000000000006</v>
+        <v>83.05</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5">
         <v>1000</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
-        <v>46282</v>
+        <v>46218</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>82.2</v>
+        <v>80.75</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>1000</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
-        <v>46289</v>
+        <v>46220</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>24</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>82.95</v>
+        <v>82.2</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7">
         <v>1000</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1">
-        <v>46289</v>
+        <v>46223</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8">
-        <v>83.3</v>
+        <v>83.4</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8">
         <v>1000</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>46271</v>
+        <v>46225</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>82.15</v>
+        <v>81.5</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9">
         <v>1000</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1">
-        <v>46273</v>
+        <v>46227</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>82.6</v>
+        <v>82.95</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10">
         <v>1000</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1">
-        <v>46278</v>
+        <v>46230</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11">
-        <v>83.05</v>
+        <v>84.1</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H11">
         <v>1000</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1">
-        <v>46285</v>
+        <v>46232</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>83.4</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12">
         <v>1000</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1">
-        <v>46292</v>
+        <v>46234</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>84.1</v>
+        <v>83.3</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13">
         <v>1000</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
